--- a/data_voor_swing/aggregatietabellen/gemeente_energiehuis.xlsx
+++ b/data_voor_swing/aggregatietabellen/gemeente_energiehuis.xlsx
@@ -19,7 +19,7 @@
     <t>gemeente</t>
   </si>
   <si>
-    <t>werkingsgebied energiehuis</t>
+    <t>energiehuis</t>
   </si>
   <si>
     <t>11001</t>
